--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_price_display.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/desktop/desktop_price_display.xlsx
@@ -452,36 +452,36 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C2" t="n">
-        <v>26.5</v>
+        <v>26.79</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Strike-through Original (Shows original price crossed out with sale price)</t>
+          <t>With Comparison (Shows similar products' prices)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="n">
-        <v>23</v>
+        <v>23.21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>With Comparison (Shows similar products' prices)</t>
+          <t>Strike-through Original (Shows original price crossed out with sale price)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>21.43</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="C5" t="n">
-        <v>19.5</v>
+        <v>19.2</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
   </sheetData>
